--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -527,6 +527,9 @@
       <c r="A11" t="str">
         <v/>
       </c>
+      <c r="C11" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -530,6 +530,9 @@
       <c r="C11" t="str">
         <v>328_卢荀草_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -588,7 +591,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515105553550</v>
+        <v>01515105553551</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -531,7 +531,7 @@
         <v>328_卢荀草_undefined_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -591,7 +591,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515105553551</v>
+        <v>015151055535510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -534,9 +534,86 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+      </c>
+      <c r="F12" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>465_羽衣甘蓝_Brassica_Brassica oleracea var. acephala DC._1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>858_桔叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>166_蜜桃雪山_Peach Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>163_咖啡时间_Coffe Break_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -591,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015151055535510</v>
+        <v>015151055535510452030100810650</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -610,6 +610,9 @@
       <c r="C21" t="str">
         <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -668,7 +671,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015151055535510452030100810650</v>
+        <v>015151055535510452030100810657</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -614,9 +614,95 @@
         <v>7</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>734_乒乓菊红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>387_洋甘菊_Chamomile_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>6</v>
+      </c>
+      <c r="C29" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -671,7 +757,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015151055535510452030100810657</v>
+        <v>015151055535510452030100810657156101020101010020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -699,6 +699,9 @@
       <c r="A31" t="str">
         <v>7</v>
       </c>
+      <c r="C31" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -702,6 +702,9 @@
       <c r="C31" t="str">
         <v>602_康乃馨白_white_undefined_20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -760,7 +763,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015151055535510452030100810657156101020101010020</v>
+        <v>015151055535510452030100810657156101020101010021</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -703,7 +703,7 @@
         <v>602_康乃馨白_white_undefined_20stems</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +763,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015151055535510452030100810657156101020101010021</v>
+        <v>0151510555355104520301008106571561010201010100213</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -706,9 +706,90 @@
         <v>13</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F34" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F35" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>260_凯拉_Kayla_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -763,7 +844,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151510555355104520301008106571561010201010100213</v>
+        <v>01515105553551045203010081065715610102010101002131053030108520100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -786,6 +786,9 @@
       <c r="C41" t="str">
         <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -844,7 +847,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515105553551045203010081065715610102010101002131053030108520100</v>
+        <v>01515105553551045203010081065715610102010101002131053030108520108</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -790,9 +790,95 @@
         <v>8</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2</v>
+      </c>
+      <c r="C43" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>143_黑巴克_Black Baccara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>3</v>
+      </c>
+      <c r="C49" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>4</v>
+      </c>
+      <c r="C50" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -847,7 +933,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515105553551045203010081065715610102010101002131053030108520108</v>
+        <v>01515105553551045203010081065715610102010101002131053030108520108101199510105100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-29.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -875,10 +875,100 @@
       <c r="A51" t="str">
         <v>5</v>
       </c>
+      <c r="C51" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F54" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>6</v>
+      </c>
+      <c r="C55" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>7</v>
+      </c>
+      <c r="C57" t="str">
+        <v>731_芍药冰点_undefined_undefined_10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>8</v>
+      </c>
+      <c r="C58" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>9</v>
+      </c>
+      <c r="C59" t="str">
+        <v>763_芍药独家记忆_undefined_undefined_10stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -933,7 +1023,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01515105553551045203010081065715610102010101002131053030108520108101199510105100</v>
+        <v>0151510555355104520301008106571561010201010100213105303010852010810119951010510531015200151002001005</v>
       </c>
     </row>
   </sheetData>
